--- a/venv/Google map/autosave_temp.xlsx
+++ b/venv/Google map/autosave_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,28 +476,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chợ Đông Ba</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>02 Trần Hưng Đạo, Phú Xuân, Huế, Việt Nam</t>
+          <t>853 Huỳnh Tấn Phát, P, Q. 07, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+842343523991</t>
+          <t>+841900232460</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>http://chodongba.com.vn/</t>
+          <t>http://www.thegioididong.com/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -508,39 +508,47 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.4726978</t>
+          <t>10.7318423</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>107.5883419</t>
+          <t>106.7317687</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+%C4%90%C3%B4ng+Ba/@16.4726978,107.5883419,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a1d58fee6cef:0xe451747b74a5dfef!8m2!3d16.4726978!4d107.5883419!16s%2Fg%2F11np7plq34?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7318423,106.7317687,17z/data=!3m1!4b1!4m6!3m5!1s0x31752564dc899d53:0x484113f86f4d6fe6!8m2!3d10.7318423!4d106.7317687!16s%2Fg%2F11csrxfyk8?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chợ An Cựu</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FJ42+W6P, Phú Nhuận, Huế, Việt Nam</t>
+          <t>7-9 Đ. Tân Mỹ, KP 2, Quận 7, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,39 +557,47 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16.4573421</t>
+          <t>10.7378518</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>107.6005738</t>
+          <t>106.7183977</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+An+C%E1%BB%B1u/@16.4573421,107.6005738,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a1f39fb71019:0xd04041181bb88e64!8m2!3d16.4573421!4d107.6005738!16s%2Fg%2F11sf5_w657!10m3!1e1!2e18!4e1?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7378518,106.7183977,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f86bcea3c8b:0xceec99331728c28a!8m2!3d10.7378518!4d106.7183977!16s%2Fg%2F11fxcgbygy?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chợ Cống</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FHCX+3PJ, Bà Triệu, Xuân Phú, Huế, Việt Nam</t>
+          <t>136 Nguyễn Thái Học, Quận 1, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/?utm_source=GMB_list&amp;utm_medium=organic&amp;utm_campaign=GMB_website</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
@@ -590,48 +606,48 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.470218</t>
+          <t>10.7691697</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>107.5992687</t>
+          <t>106.6950012</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+C%E1%BB%91ng/@16.470218,107.5992687,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a118178c899d:0x2cefd50a280b8e04!8m2!3d16.470218!4d107.5992687!16s%2Fg%2F1hc0w66zr?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7691697,106.6950012,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f3e0d41ad9f:0xf647dd4ad9193b06!8m2!3d10.7691697!4d106.6950012!16s%2Fg%2F1yfh_kpqy?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chợ Đầu mối Phú Hậu</t>
+          <t>Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FHRP+JJR, Nguyễn Gia Thiều, Phú Hiệp, Huế, Việt Nam</t>
+          <t>311A Huỳnh Tấn Phát, Quận 7, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/chodaumoi76/</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t></t>
-        </is>
-      </c>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>{}</t>
@@ -639,45 +655,45 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16.4916174</t>
+          <t>10.7513552</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>107.5865152</t>
+          <t>106.7287391</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+%C4%90%E1%BA%A7u+m%E1%BB%91i+Ph%C3%BA+H%E1%BA%ADu/@16.4916174,107.5865152,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a0d1d8e53a31:0x5198c796628d8f80!8m2!3d16.4916174!4d107.5865152!16s%2Fg%2F11gd1vw1c0?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7513552,106.7287391,17z/data=!3m1!4b1!4m6!3m5!1s0x317525869aa85e3b:0xe4ee22eec38ef59f!8m2!3d10.7513552!4d106.7287391!16s%2Fg%2F1ptvzgqn_?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chợ Vĩ Dạ</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>187 Nguyễn Sinh Cung, Vỹ Dạ, Huế, Việt Nam</t>
+          <t>468 Đ. Nguyễn Thị Thập, Tân Quy, Quận 7, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+842343825432</t>
+          <t>+841900232460</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://vietinterfoods.com/products/nuoc-tuong-nhat-ban-s2-bep-yeu</t>
+          <t>https://www.thegioididong.com/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -688,44 +704,48 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16.4829494</t>
+          <t>10.7395631</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>107.5959809</t>
+          <t>106.7066666</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+V%C4%A9+D%E1%BA%A1/@16.4829494,107.5959809,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a0dfba1e3da1:0x2b100373fa23e35!8m2!3d16.4829494!4d107.5959809!16s%2Fg%2F1hc3ysjhq?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7395631,106.7066666,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f9b4d256ac7:0x6020ef8ad184b207!8m2!3d10.7395631!4d106.7066666!16s%2Fg%2F11j1hxxgp7?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chợ An Hòa</t>
+          <t>Siêu thị Thế Giới Di Động (Trung Tâm Laptop)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>34 Đặng Tất, tổ 11, An Hòa, Huế, Việt Nam</t>
+          <t>138 Khánh Hội, Phường 9, Quận 4, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t></t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>{}</t>
@@ -733,39 +753,47 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.4815889</t>
+          <t>10.7574861</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>107.557393</t>
+          <t>106.70024</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+An+H%C3%B2a/@16.4815889,107.557393,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a6d8d8f056df:0xdc721160f301b28f!8m2!3d16.4815889!4d107.557393!16s%2Fg%2F11c5szn5v5?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+(Trung+T%C3%A2m+Laptop)/@10.7574861,106.70024,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f6d5733f469:0xae0671d5491bea1c!8m2!3d10.7574861!4d106.70024!16s%2Fg%2F11b6x5k2v7?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chợ Xép Thuận Lộc</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FHHJ+GXF, Nhật Lệ, Thuận Thành, Huế, Việt Nam</t>
+          <t>179 Đ. Tôn Đản, P. 15, Q. 04, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
@@ -774,39 +802,47 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16.4788143</t>
+          <t>10.7578102</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>107.5824073</t>
+          <t>106.7065722</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+X%C3%A9p+Thu%E1%BA%ADn+L%E1%BB%99c/@16.4788143,107.5824073,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a12911909ba3:0x72c96628612995da!8m2!3d16.4788143!4d107.5824073!16s%2Fg%2F1hc329mh3?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7578102,106.7065722,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f6e1248a29d:0x27d8bf435caae0df!8m2!3d10.7578102!4d106.7065722!16s%2Fg%2F11byxgykkv?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chợ Quê Cầu Ngói Thanh Toàn</t>
+          <t>Thế Giới Di Động (CN Nguyễn Thị Minh Khai).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FJ8V+F5P, Lang Xá Bàu, Hương Thủy, Huế, Việt Nam</t>
+          <t>145 Nguyễn Thị Minh Khai, Bến Thành, Quận 1, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
@@ -815,39 +851,47 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16.4662116</t>
+          <t>10.7710756</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>107.6429677</t>
+          <t>106.6872107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+Qu%C3%AA+C%E1%BA%A7u+Ng%C3%B3i+Thanh+To%C3%A0n/@16.4662116,107.6429677,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a16a490997d9:0x839c76e83288d310!8m2!3d16.4662116!4d107.6429677!16s%2Fg%2F11gl5b9p5z?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+(CN+Nguy%E1%BB%85n+Th%E1%BB%8B+Minh+Khai)./@10.7710756,106.6872107,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f4b2e628c4f:0x17b7504507484a6e!8m2!3d10.7710756!4d106.6872107!16s%2Fg%2F11bw5thk7l?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chợ Bao Vinh</t>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FHWG+MHC, 105 Bao Vinh, Hương Vang, Hương Trà, Huế, Việt Nam</t>
+          <t>228A-230 Đ3 Tháng 2, Phường 12, Quận 10, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
@@ -856,44 +900,48 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.496596</t>
+          <t>10.7741632</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>107.5763788</t>
+          <t>106.6776504</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+Bao+Vinh/@16.496596,107.5763788,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a19560c701b9:0x9c8cc6aaa64b2798!8m2!3d16.496596!4d107.5763788!16s%2Fg%2F11pttkpz54!10m3!1e1!2e18!4e1?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7741632,106.6776504,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f20ca82667b:0x38c771523c657145!8m2!3d10.7741632!4d106.6776504!16s%2Fg%2F1q5hrfhpn?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chợ Vinh Thanh Huế</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CQJM+F3C, Chợ, Phú Vang, Huế, Việt Nam</t>
+          <t>158 Phạm Hữu Lầu, Phú Mỹ, Quận 7, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t></t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>{}</t>
@@ -901,41 +949,45 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16.4311864</t>
+          <t>10.7044903</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>107.7826428</t>
+          <t>106.7312737</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+Vinh+Thanh+Hu%E1%BA%BF/@16.4311864,107.7826428,17z/data=!3m1!4b1!4m6!3m5!1s0x31419c120c8575d9:0x3d82020ae76e151b!8m2!3d16.4311864!4d107.7826428!16s%2Fg%2F11c1pm6f59?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7044903,106.7312737,17z/data=!3m1!4b1!4m6!3m5!1s0x3175253bc3f5ff4f:0x9f2589c28f785e35!8m2!3d10.7044903!4d106.7312737!16s%2Fg%2F11q90b1l4m?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chợ Mỹ Lợi</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9VH3+FQ5, Vinh Mỹ, Phú Lộc, Huế, Việt Nam</t>
+          <t>1787 Huỳnh Tấn Phát, Nhà Bè, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>http://www.hue.vnn.vn/vi/53/2565/Di-tich-%E2%80%93-Danh-thang/Co-tich-My-Loi.html#.WAmAivmLSiM</t>
+          <t>http://www.thegioididong.com/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -946,45 +998,45 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16.3773113</t>
+          <t>10.7013858</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>107.8528127</t>
+          <t>106.7383213</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+M%E1%BB%B9+L%E1%BB%A3i/@16.3773113,107.8528127,17z/data=!3m1!4b1!4m6!3m5!1s0x31419b2dd9428dc7:0x3e0b96e1c85be7c!8m2!3d16.3773113!4d107.8528127!16s%2Fg%2F1tlk8w5l?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7013858,106.7383213,17z/data=!3m1!4b1!4m6!3m5!1s0x3175254ce0408103:0x2300106c0b06fee1!8m2!3d10.7013858!4d106.7383213!16s%2Fg%2F11bx1qbxx2?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chợ Chiều Vinh Thanh</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phú Vinh, Phú Vang, Huế, Việt Nam</t>
+          <t>190B Nguyễn Thị Định, An Phú, Q. 02, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+84387117714</t>
+          <t>+841900232460</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://l.facebook.com/l.php?u=https%3A%2F%2Ftiktok.com%2F%40andanxedanang.com%3Ffbclid%3DIwZXh0bgNhZW0CMTAAYnJpZBEwQkJkeVN0ck1TclQxOFJLRHNydGMGYXBwX2lkEDIyMjAzOTE3ODgyMDA4OTIAAR5HcZ7jP3xROwjZ_Bt36L484oDuUlV1F5nTh-d688hoRD67BSwIlmXSfUyG6w_aem_Thus61OJS3httv3zzfnoLA&amp;h=AT2SpMhK1ZJfWpI5bbQpXIDPGC3hpa-wv4DXcya6Cfcdrs7dcr7Coqdu8GO_UGc4P_M0uVI8-1zNnndEl2YqJtSsYLdrO8A7xh525wZSLYzBWw4PyGRfsQaEHn2EY6q9j6FT</t>
+          <t>http://www.thegioididong.com/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -995,39 +1047,47 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16.4375516</t>
+          <t>10.7904314</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>107.7813493</t>
+          <t>106.7542751</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+Chi%E1%BB%81u+Vinh+Thanh/@16.4375516,107.7813493,17z/data=!3m1!4b1!4m6!3m5!1s0x31419c14032bd8b1:0xa628e7707fcc384a!8m2!3d16.4375516!4d107.7813493!16s%2Fg%2F11c1szsz5y?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7904314,106.7542751,17z/data=!3m1!4b1!4m6!3m5!1s0x31752676be724c67:0xcbc54e62ff8742a7!8m2!3d10.7904314!4d106.7542751!16s%2Fg%2F11btmqcvc2?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chợ Bến Ngự</t>
+          <t>Siêu Thị Thế Giới Di Động Hưng Phú Quận 8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FH4M+3GM, Phan Bội Châu, Vĩnh Ninh, Huế, Việt Nam</t>
+          <t>733 Đ. Hưng Phú, Phường 9, Q. 08, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
@@ -1036,39 +1096,47 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16.4552874</t>
+          <t>10.7458348</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>107.5838974</t>
+          <t>106.6673809</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+B%E1%BA%BFn+Ng%E1%BB%B1/@16.4552874,107.5838974,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a10066cc1c3b:0xda3ef78f622eb984!8m2!3d16.4552874!4d107.5838974!16s%2Fg%2F11yfthyxp6!10m3!1e1!2e18!4e1?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+Th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+H%C6%B0ng+Ph%C3%BA+Qu%E1%BA%ADn+8/@10.7458348,106.6673809,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e57b4f3efc5:0xd2da01d2b8075920!8m2!3d10.7458348!4d106.6673809!16s%2Fg%2F11c329dvhn?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chợ Huế</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>37 kiet 82 Nguyễn Gia Thiều, Phú Hiệp, Huế, Việt Nam</t>
+          <t>128 Trần Quang Khải, Tân Định, Quận 1, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+842838102102</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
@@ -1077,45 +1145,45 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16.4935937</t>
+          <t>10.7921819</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>107.5818119</t>
+          <t>106.6918383</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+Hu%E1%BA%BF/@16.4935937,107.5818119,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a10026af718b:0xa9aa43f4599f56ec!8m2!3d16.4935937!4d107.5818119!16s%2Fg%2F11ms_mltzn?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7921819,106.6918383,17z/data=!3m1!4b1!4m6!3m5!1s0x317528ccf737716f:0xcb01e5cd868acab6!8m2!3d10.7921819!4d106.6918383!16s%2Fg%2F11b6x87_dm?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Muse Dress - Cho Thuê Váy Thiết Kế, Áo Dài ở Huế</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>39 Trần Phú, Thuận Hóa, Huế, 530000, Việt Nam</t>
+          <t>191 Điện Biên Phủ, P. 06, Q. 03, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+84702187321</t>
+          <t>+841900232460</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61580975923509</t>
+          <t>http://www.thegioididong.com/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1126,39 +1194,47 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16.4548315</t>
+          <t>10.7862492</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>107.5923026</t>
+          <t>106.693764</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Muse+Dress+-+Cho+Thu%C3%AA+V%C3%A1y+Thi%E1%BA%BFt+K%E1%BA%BF,+%C3%81o+D%C3%A0i+%E1%BB%9F+Hu%E1%BA%BF/@16.4548315,107.5923026,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a16781f1179b:0x7f6919e4bec1fd7b!8m2!3d16.4548315!4d107.5923026!16s%2Fg%2F11n9dt0rl_?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7862492,106.693764,17z/data=!3m1!4b1!4m6!3m5!1s0x317528a53cfc8849:0x77d5261184097a1!8m2!3d10.7862492!4d106.693764!16s%2Fg%2F11b7y7z1n3?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chợ phường Phường Đúc</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FH37+GWM, Bùi Thị Xuân, Phường Đúc, Huế, Việt Nam</t>
+          <t>Đ. Phạm Hùng, Ấp 4A, Bình Chánh, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
@@ -1167,39 +1243,47 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16.4538405</t>
+          <t>10.7336823</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>107.5647998</t>
+          <t>106.6737052</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+ph%C6%B0%E1%BB%9Dng+Ph%C6%B0%E1%BB%9Dng+%C4%90%C3%BAc/@16.4538405,107.5647998,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a6b0dd89a4b7:0x42cd90d6b6bf7db0!8m2!3d16.4538405!4d107.5647998!16s%2Fg%2F11b67gdb30?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7336823,106.6737052,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e4d018b9829:0xa671c184a0f1cead!8m2!3d10.7336823!4d106.6737052!16s%2Fg%2F1pp2v1lwp?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chợ An Xuân</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HH53+MW7, Thôn, Quảng An, Quảng Điền, Huế, Việt Nam</t>
+          <t>176 Nguyễn Tri Phương, Quận 5, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
@@ -1208,39 +1292,47 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.5597023</t>
+          <t>10.7595684</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>107.5547477</t>
+          <t>106.6691319</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+An+Xu%C3%A2n/@16.5597023,107.5547477,17z/data=!3m1!4b1!4m6!3m5!1s0x3141090066112789:0x47144207729ade95!8m2!3d16.5597023!4d107.5547477!16s%2Fg%2F11ln2smbll!10m3!1e1!2e18!4e1?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7595684,106.6691319,17z/data=!3m1!4b1!4m6!3m5!1s0x31752ee495ea3593:0x5008c89bfecbc40c!8m2!3d10.7595684!4d106.6691319!16s%2Fg%2F11b6x5pk2q?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chợ tay ba</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FH7R+F8Q, Thuận Hóa, Huế, Việt Nam</t>
+          <t>Duong Ba Trac, Quận 8, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
@@ -1249,44 +1341,48 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.4637117</t>
+          <t>10.744484</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>107.5908628</t>
+          <t>106.6888912</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+tay+ba/@16.4637117,107.5908628,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a1508c1d072f:0x9dced63a4736b941!8m2!3d16.4637117!4d107.5908628!16s%2Fg%2F11ryqm0gjs!10m3!1e1!2e18!4e1?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.744484,106.6888912,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f0625d4de41:0x9b6d5b28fdbecf00!8m2!3d10.744484!4d106.6888912!16s%2Fg%2F11hylcyjw4?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Phố tây Huế</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>29 Chu Văn An, Phú Hội, Huế, Việt Nam</t>
+          <t>176 Đ. Hải Thượng Lãn Ông, Phường 10, Q. 05, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t></t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1294,48 +1390,48 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.4698247</t>
+          <t>10.7507742</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>107.5953926</t>
+          <t>106.6596364</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ph%E1%BB%91+t%C3%A2y+Hu%E1%BA%BF/@16.4698247,107.5953926,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a122d30ecfe7:0xbe50922a30dc55c5!8m2!3d16.4698247!4d107.5953926!16s%2Fg%2F11fyxb85td?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7507742,106.6596364,17z/data=!3m1!4b1!4m6!3m5!1s0x31752ef68935463b:0x38f19834a238ebee!8m2!3d10.7507742!4d106.6596364!16s%2Fg%2F11b7y0d5tz?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Đường đi bộ Nguyễn Đình Chiểu</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nguyễn Đình Chiểu, Phú Hội, Huế, Việt Nam</t>
+          <t>198 Trần Não, ấp Bình Khánh 2, P. Bình An, Q. 02, Thành phố Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>http://facebook.com/PhodiboNDC</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t></t>
-        </is>
-      </c>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1343,39 +1439,47 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16.466961</t>
+          <t>10.7900207</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>107.5890376</t>
+          <t>106.7299594</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/%C4%90%C6%B0%E1%BB%9Dng+%C4%91i+b%E1%BB%99+Nguy%E1%BB%85n+%C4%90%C3%ACnh+Chi%E1%BB%83u/@16.466961,107.5890376,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a13b07b771ab:0xafdcf6ed1832757e!8m2!3d16.466961!4d107.5890376!16s%2Fg%2F11bz0xt2jc?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7900207,106.7299594,17z/data=!3m1!4b1!4m6!3m5!1s0x3175260739d15971:0x8da66800cafb9520!8m2!3d10.7900207!4d106.7299594!16s%2Fg%2F11cmtb2vh8?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHỢ VĨNH TU</t>
+          <t>Siêu thị Thế giới Di động</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JGFC+W7X, Thôn Vĩnh Tu, Quảng Điền, Huế, Việt Nam</t>
+          <t>482 Đ. Hồng Bàng, Phường 16, Quận 11, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
@@ -1384,43 +1488,47 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16.6248623</t>
+          <t>10.7539508</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>107.5207472</t>
+          <t>106.6479478</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/CH%E1%BB%A2+V%C4%A8NH+TU/@16.6248623,107.5207472,17z/data=!3m1!4b1!4m6!3m5!1s0x31410faf97ad3d75:0xda83f2c7c3f45a02!8m2!3d16.6248623!4d107.5207472!16s%2Fg%2F11l5l4c6g4?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+gi%E1%BB%9Bi+Di+%C4%91%E1%BB%99ng/@10.7539508,106.6479478,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e8bf5eeadb5:0xe89592269bd4d04c!8m2!3d10.7539508!4d106.6479478!16s%2Fg%2F11b682t0bd?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vincom Plaza Huế</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>50A Hùng Vương, Phú Nhuận, Huế, Việt Nam</t>
+          <t>602/1 Điện Biên Phủ, Phường 22, Bình Thạnh, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+84981329408</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
@@ -1429,43 +1537,47 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16.4631061</t>
+          <t>10.7989174</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>107.5945241</t>
+          <t>106.7179845</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Vincom+Plaza+Hu%E1%BA%BF/@16.4631061,107.5945241,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a13e8ec40d09:0xc669dbfc2743e474!8m2!3d16.4631061!4d107.5945241!16s%2Fg%2F11f3g4lc_5?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7989174,106.7179845,17z/data=!3m1!4b1!4m6!3m5!1s0x317528a601719f55:0xe955ce4c6e7f42b4!8m2!3d10.7989174!4d106.7179845!16s%2Fg%2F11df2ymm69?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BÚN BÒ HUẾ CÔ XUÂN CHỢ ĐÔNG BA - QUẬN 7</t>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>72 Đường số 79, Tân Quy, Quận 7, Hồ Chí Minh, Việt Nam</t>
+          <t>75-77 Đ. Lê Văn Sỹ, P. 13, Phú Nhuận, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>+84978930807</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
@@ -1474,52 +1586,48 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10.7400244</t>
+          <t>10.7908962</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>106.7098293</t>
+          <t>106.6726844</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/B%C3%9AN+B%C3%92+HU%E1%BA%BE+C%C3%94+XU%C3%82N+CH%E1%BB%A2+%C4%90%C3%94NG+BA+-+QU%E1%BA%ACN+7/@10.7400244,106.7098293,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f006407c851:0x76c69a6ec7c3b44b!8m2!3d10.7400244!4d106.7098293!16s%2Fg%2F11vxpsxyxw?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7908962,106.6726844,17z/data=!3m1!4b1!4m6!3m5!1s0x3175292b2d8c0d7d:0x242b5553d45957fe!8m2!3d10.7908962!4d106.6726844!16s%2Fg%2F11cnch6b8z?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cho thuê xe máy điện tại Huế - Trần Hoàng</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>86 Lê Duẩn, Phú Hoà, Huế, 49000, Việt Nam</t>
+          <t>153B Phan Đăng Lưu, P. 02, Phú Nhuận, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+84978953953</t>
+          <t>+841900232460</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>http://chothuexemaydien.com/</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t></t>
-        </is>
-      </c>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1527,45 +1635,45 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16.466918</t>
+          <t>10.8017765</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>107.5822994</t>
+          <t>106.6832631</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Cho+thu%C3%AA+xe+m%C3%A1y+%C4%91i%E1%BB%87n+t%E1%BA%A1i+Hu%E1%BA%BF+-+Tr%E1%BA%A7n+Ho%C3%A0ng/@16.466918,107.5822994,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a17626fa9f3d:0xd00f58f0757c6a9!8m2!3d16.466918!4d107.5822994!16s%2Fg%2F11ty461d3n?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8017765,106.6832631,17z/data=!3m1!4b1!4m6!3m5!1s0x317528da11973445:0x69b47cfad3d67cfe!8m2!3d10.8017765!4d106.6832631!16s%2Fg%2F11b6nrdmd1?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AEON MALL Huế</t>
+          <t>Siêu thị Điện máy XANH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8 Võ Nguyên Giáp, An Đông, Huế, Việt Nam</t>
+          <t>428 Đ. Nguyễn Thị Thập, Tân Quy, Quận 7, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>+842343886888</t>
+          <t>+841900232461</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>http://hue.aeonmall-vietnam.com/</t>
+          <t>https://www.dienmayxanh.com/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1576,45 +1684,45 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16.4544777</t>
+          <t>10.7393481</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>107.6142133</t>
+          <t>106.7088406</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/AEON+MALL+Hu%E1%BA%BF/@16.4544777,107.6142133,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a10055eabfaf:0x9627c56093af6213!8m2!3d16.4544777!4d107.6142133!16s%2Fg%2F11y4ydvxjf?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%90i%E1%BB%87n+m%C3%A1y+XANH/@10.7393481,106.7088406,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f9b78af10b7:0x18a51aa71277427b!8m2!3d10.7393481!4d106.7088406!16s%2Fg%2F11c5hjkd8j?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shop Hoa Tươi Chợ Vĩ Dạ - Hoa 4 Leaf Clover</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20 Hà Nội, Phú Nhuận, Huế, Việt Nam</t>
+          <t>27 Quốc Hương, Khu Phố 4, Thủ Đức, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+84825634234</t>
+          <t>+841900232460</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/shophoa4cleaflover</t>
+          <t>http://thegioididong.com/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1625,45 +1733,45 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16.4637439</t>
+          <t>10.8032965</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>107.5926519</t>
+          <t>106.7318729</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Shop+Hoa+T%C6%B0%C6%A1i+Ch%E1%BB%A3+V%C4%A9+D%E1%BA%A1+-+Hoa+4+Leaf+Clover/@16.4637439,107.5926519,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a14af1306665:0xcea8f084ace0cb58!8m2!3d16.4637439!4d107.5926519!16s%2Fg%2F11myq568gg?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8032965,106.7318729,17z/data=!3m1!4b1!4m6!3m5!1s0x3175261afc703ae7:0x200dbed1a8c5435d!8m2!3d10.8032965!4d106.7318729!16s%2Fg%2F11c5s48zvl?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cho Thuê Xe máy Huế</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22/4 Hà Nội, Phú Nhuận, Huế, 52000, Việt Nam</t>
+          <t>346 Đ. Phạm Văn Chí, Phường 4, Quận 6, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>+84777529259</t>
+          <t>+841900232460</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>http://thuexemayngaden.com/</t>
+          <t>https://www.thegioididong.com/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1674,39 +1782,47 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16.4633602</t>
+          <t>10.743691</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>107.5928865</t>
+          <t>106.644405</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Cho+Thu%C3%AA+Xe+m%C3%A1y+Hu%E1%BA%BF/@16.4633602,107.5928865,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a17c166560ef:0x5f3f694cf0a8a6!8m2!3d16.4633602!4d107.5928865!16s%2Fg%2F11t05tbvp3?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.743691,106.644405,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e6385c94baf:0xaff347ce4db12684!8m2!3d10.743691!4d106.644405!16s%2Fg%2F11cs31s9gj?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>O huệ cung cấp cá nước lợ và hải sản tươi sống</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chợ phù bài (thủy phù) thôn 9, Huế, Việt Nam</t>
+          <t>1680 Phạm Thế Hiển, Phường 6, Quận 8, Hồ Chí Minh 70000, Việt Nam</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
@@ -1715,39 +1831,47 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16.4637117</t>
+          <t>10.7393451</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>107.5908628</t>
+          <t>106.6532638</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/O+hu%E1%BB%87+cung+c%E1%BA%A5p+c%C3%A1+n%C6%B0%E1%BB%9Bc+l%E1%BB%A3+v%C3%A0+h%E1%BA%A3i+s%E1%BA%A3n+t%C6%B0%C6%A1i+s%E1%BB%91ng/@16.4637117,107.5908628,17z/data=!3m1!4b1!4m6!3m5!1s0x3141a1f26f86591d:0xefe23071dd7b8a33!8m2!3d16.4637117!4d107.5908628!16s%2Fg%2F11pzhhj2q9?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7393451,106.6532638,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e5d70f60779:0x5d45d480fc79baf5!8m2!3d10.7393451!4d106.6532638!16s%2Fg%2F11c5sgtfxb?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>chợ ở Huế</t>
+          <t>siêu thị thế giới di động ở sài gòn</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chợ Hai Bà Trưng</t>
+          <t>Siêu thị Thế Giới Di Động</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12 kiet 23 Hai Bà Trưng, Vĩnh Ninh, Huế, Việt Nam</t>
+          <t>1273 Đ3 Tháng 2, P. 06, Quận 11, Hồ Chí Minh 700000, Việt Nam</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
@@ -1756,17 +1880,4415 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16.46184</t>
+          <t>10.7590363</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>107.5897433</t>
+          <t>106.6514795</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%E1%BB%A3+Hai+B%C3%A0+Tr%C6%B0ng/data=!4m7!3m6!1s0x3141a1391d2798ad:0xf502e28b0193b17f!8m2!3d16.46184!4d107.5897433!16s%2Fg%2F1tfj0n5d!19sChIJrZgnHTmhQTERf7GTAYviAvU?authuser=0&amp;hl=vi&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7590363,106.6514795,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e8d5fa46ef7:0xb7829cb17887315d!8m2!3d10.7590363!4d106.6514795!16s%2Fg%2F11bccmtww5?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>121 -123 Đ. Võ Văn Ngân, Phường, Thủ Đức, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10.8506576</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>106.76073</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8506576,106.76073,17z/data=!3m1!4b1!4m6!3m5!1s0x317527a2bd576c51:0x53b5194b7979d83!8m2!3d10.8506576!4d106.76073!16s%2Fg%2F1tf7d4t4?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động (Trung Tâm Laptop)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>246 Đ. Đỗ Xuân Hợp, Phước Long B, Thủ Đức, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10.8245413</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>106.7690804</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+(Trung+T%C3%A2m+Laptop)/@10.8245413,106.7690804,17z/data=!3m1!4b1!4m6!3m5!1s0x31752655c1ae970d:0xe699261add409b11!8m2!3d10.8245413!4d106.7690804!16s%2Fg%2F11r96b2ln?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>270B Đ. Lý Thường Kiệt, Phường 6, Tân Bình, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10.7783044</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>106.65634</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7783044,106.65634,17z/data=!3m1!4b1!4m6!3m5!1s0x31752ec640bfa7b9:0x935a3b05eee6d2f0!8m2!3d10.7783044!4d106.65634!16s%2Fg%2F11b77qb_55?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>98 Đ. Minh Phụng, Phường 2, Quận 6, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>+842838102102</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10.749965</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>106.6425547</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.749965,106.6425547,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e8f247dcd99:0x8132526887f2f6e3!8m2!3d10.749965!4d106.6425547!16s%2Fg%2F11bwpz7mvk?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Thế giới di động (CN 708 Nguyễn Trãi).</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>708 Nguyễn Trãi, Phường 11, Quận 5, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10.753324</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>106.6612267</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+gi%E1%BB%9Bi+di+%C4%91%E1%BB%99ng+(CN+708+Nguy%E1%BB%85n+Tr%C3%A3i)./@10.753324,106.6612267,17z/data=!3m1!4b1!4m6!3m5!1s0x31752ef72a923d35:0x94f83c3e525997ce!8m2!3d10.753324!4d106.6612267!16s%2Fg%2F1tj2kz8b?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Số 73 đường Nguyễn Văn Cừ, KP. 3, TT. An Thới, H. Phú Quốc, T. Kiên Giang, Kiên Giang, 920000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>+842838102102</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10.7557429</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>106.6853664</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7557429,106.6853664,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f051ee352af:0xb54489504ed8cb6b!8m2!3d10.7557429!4d106.6853664!16s%2Fg%2F11c6rb30ry?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>304 Tô Hiến Thành, Phường 15, Quận 10, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10.7767668</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>106.6635911</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7767668,106.6635911,17z/data=!3m1!4b1!4m6!3m5!1s0x31752ec4c50ac6c9:0x1c9a7f935b5d3e2f!8m2!3d10.7767668!4d106.6635911!16s%2Fg%2F11b6nx6ddb?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>820 Xô Viết Nghệ Tĩnh, Phường 25, Bình Thạnh, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10.8124085</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>106.7156434</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8124085,106.7156434,17z/data=!3m1!4b1!4m6!3m5!1s0x31752898e3ffc7ad:0x9a274cecd641d743!8m2!3d10.8124085!4d106.7156434!16s%2Fg%2F11c55vwnzy?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3 Đ. Kinh Dương Vương, Phường 12, Quận 6, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10.7534195</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>106.6341816</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7534195,106.6341816,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e8138a0252d:0xbf69c1e976b70652!8m2!3d10.7534195!4d106.6341816!16s%2Fg%2F11bw51sxx3?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>307B Lê Quang Định, P. 07, Bình Thạnh, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10.8108767</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>106.691433</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8108767,106.691433,17z/data=!3m1!4b1!4m6!3m5!1s0x317528c27c925eef:0xba7f20e8808a7dd7!8m2!3d10.8108767!4d106.691433!16s%2Fg%2F11bw8dmvw9?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động (Luxury Store)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bên phải/359 Đ. Lê Văn Sỹ, Tân Bình, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10.7966136</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>106.6647344</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+(Luxury+Store)/@10.7966136,106.6647344,17z/data=!3m1!4b1!4m6!3m5!1s0x3175292e07283a97:0x12cdb3a9333e3a25!8m2!3d10.7966136!4d106.6647344!16s%2Fg%2F11b6xh5sr2?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>56A Đ. Lê Quang Sung, P. 02, Q. 06, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10.7511632</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>106.650304</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7511632,106.650304,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e8b1d67646f:0xcc944a4492ba82de!8m2!3d10.7511632!4d106.650304!16s%2Fg%2F11b5phxw9m?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>319-321 Liên Tỉnh 5, Phường Bình Đông, Quận 8, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10.7342368</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>106.6563714</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7342368,106.6563714,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e43a62a8fd5:0x25f420208e1d1911!8m2!3d10.7342368!4d106.6563714!16s%2Fg%2F1tfzpdmg?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>171 Nguyễn Sơn, P, Tân Phú, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10.7825625</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>106.6270395</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7825625,106.6270395,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c02d0d43199:0xd80bec43dbb36b79!8m2!3d10.7825625!4d106.6270395!16s%2Fg%2F1hc1msp50?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>233 Nơ Trang Long, Phường 11, Bình Thạnh, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10.817027</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>106.6976996</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.817027,106.6976996,17z/data=!3m1!4b1!4m6!3m5!1s0x317528ec900325bd:0xc0b8f83d3746705e!8m2!3d10.817027!4d106.6976996!16s%2Fg%2F11b6xdnb4p?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>281K Lãnh Binh Thăng, P. 08, Quận 11, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>+842838102102</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10.7636912</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>106.6491995</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7636912,106.6491995,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e93996da573:0xd564bcce59d69f1c!8m2!3d10.7636912!4d106.6491995!16s%2Fg%2F11bw1wmn0m?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B6, Ấp 2/192 Văn Tiến Dũng, Phong Phú, Bình Chánh, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10.6909941</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>106.6548516</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.6909941,106.6548516,17z/data=!3m1!4b1!4m6!3m5!1s0x317531c2f7c473ff:0x7beca960ea3d10f9!8m2!3d10.6909941!4d106.6548516!16s%2Fg%2F11csr62lhr?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>332 Cộng Hòa, Tân Bình, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10.8022436</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>106.6458303</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8022436,106.6458303,17z/data=!3m1!4b1!4m6!3m5!1s0x3175294f71d9cb83:0x60ecc45a67f532e5!8m2!3d10.8022436!4d106.6458303!16s%2Fg%2F11c543lj63?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>159 –161 Đ. Lê Văn Việt, Hiệp Phú, Thủ Đức, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10.8458306</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>106.7791189</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8458306,106.7791189,17z/data=!3m1!4b1!4m6!3m5!1s0x3175270c6fa8425f:0x2721b510c3d0ff90!8m2!3d10.8458306!4d106.7791189!16s%2Fg%2F1wc45h0t?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>670 Âu Cơ, Phường 10, Tân Bình, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10.7859525</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>106.6417651</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7859525,106.6417651,17z/data=!3m1!4b1!4m6!3m5!1s0x31752eb1e8b0c877:0x356fd0f18daf50ac!8m2!3d10.7859525!4d106.6417651!16s%2Fg%2F11xmdml85?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>259 Phan Huy Ích, Phường 14, Gò Vấp, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10.8358855</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>106.6354635</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8358855,106.6354635,17z/data=!3m1!4b1!4m6!3m5!1s0x31752978a925a9d7:0xad84b8099b8a120e!8m2!3d10.8358855!4d106.6354635!16s%2Fg%2F1ptxp87z0?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>159 Đ. Thạch Lam, Phú Thạnh, Tân Phú, Thành phố Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10.7774753</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>106.6286471</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7774753,106.6286471,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c1df0f268c9:0xce6943013111018f!8m2!3d10.7774753!4d106.6286471!16s%2Fg%2F11c55v87hs?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A11/1 Ấp 2, Bình Hưng, Bình Chánh, Thành phố Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10.7267859</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>106.6558079</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7267859,106.6558079,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e408633181b:0xd1d919332f8f9832!8m2!3d10.7267859!4d106.6558079!16s%2Fg%2F11c2nktgr7?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>292 Âu Cơ, Phường 10, Tân Bình, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10.7748846</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>106.6482682</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7748846,106.6482682,17z/data=!3m1!4b1!4m6!3m5!1s0x31752ebeb8a7f505:0xe5c0737a94e07983!8m2!3d10.7748846!4d106.6482682!16s%2Fg%2F11d_d2z2b0?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>848 Lạc Long Quân, P. 08, Tân Bình, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10.7794491</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>106.6499807</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7794491,106.6499807,17z/data=!3m1!4b1!4m6!3m5!1s0x31752eb84ae38481:0x2cce7af0568deb8!8m2!3d10.7794491!4d106.6499807!16s%2Fg%2F11xg6y4j4?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động (Trung tâm Laptop)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1077 Đ. Hậu Giang, Phường 11, Quận 6, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10.7450307</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>106.624058</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+(Trung+t%C3%A2m+Laptop)/@10.7450307,106.624058,17z/data=!3m1!4b1!4m6!3m5!1s0x31752dd41026afe9:0x6fd88b42bd53f2d6!8m2!3d10.7450307!4d106.624058!16s%2Fg%2F11b6dpnx4k?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>222 Đ. Trường Chinh, Đông Hưng Thuận, Quận 12, Thành phố Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10.8312551</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>106.6229594</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8312551,106.6229594,17z/data=!3m1!4b1!4m6!3m5!1s0x31752bd152505e0d:0x2dd7755ccc4b79bc!8m2!3d10.8312551!4d106.6229594!16s%2Fg%2F11c6v9qwky?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1316 Nguyễn Duy Trinh, Long Trường, Thủ Đức, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10.8048837</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>106.8163645</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8048837,106.8163645,17z/data=!3m1!4b1!4m6!3m5!1s0x317526ca9e5d0d65:0xa33f58b66f281ae5!8m2!3d10.8048837!4d106.8163645!16s%2Fg%2F11c1p5x0y8?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>252-254 Đ3 Tháng 2, Phường 12, Quận 10, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/?utm_source=GMB_list&amp;utm_medium=organic&amp;utm_campaign=GMB_website</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10.7708347</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>106.6725905</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7708347,106.6725905,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f859ae2006d:0xcb96f1ed33852bb4!8m2!3d10.7708347!4d106.6725905!16s%2Fg%2F11jz3l206z?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Thế giới di động</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1036 Đ. Tân Kỳ Tân Quý, Bình Hưng Hoà, Bình Tân, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10.7897897</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>106.5960467</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+gi%E1%BB%9Bi+di+%C4%91%E1%BB%99ng/@10.7897897,106.5960467,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c70d20ccf9b:0x9c19fb205fa921c9!8m2!3d10.7897897!4d106.5960467!16s%2Fg%2F1tdh5ypj?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1A Phan Huy Ích, Phường 15, Tân Bình, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10.8236166</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>106.6297766</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8236166,106.6297766,17z/data=!3m1!4b1!4m6!3m5!1s0x31752962844a5f09:0x5b68d7a5b85e75b3!8m2!3d10.8236166!4d106.6297766!16s%2Fg%2F11c55stj0r?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Đại Phước, Nhơn Trạch, Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10.7355236</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>106.8171425</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7355236,106.8171425,17z/data=!3m1!4b1!4m6!3m5!1s0x31752481de86b243:0x3719ae1855375615!8m2!3d10.7355236!4d106.8171425!16s%2Fg%2F11fx8hyl88?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>104 Đ. Hòa Bình, Phường 3, Tân Phú, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10.7696921</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>106.6357587</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7696921,106.6357587,17z/data=!3m1!4b1!4m6!3m5!1s0x31752e98b77639ff:0x1cfdd9045ea153f2!8m2!3d10.7696921!4d106.6357587!16s%2Fg%2F11bw8dpq_5?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động 1024 Hương Lộ 2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1024 HL2, Bình Hưng Hoà B, Bình Tân, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10.7699776</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>106.5915894</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+1024+H%C6%B0%C6%A1ng+L%E1%BB%99+2/@10.7699776,106.5915894,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c5ce5475531:0xb0aa9fc87cee6d9a!8m2!3d10.7699776!4d106.5915894!16s%2Fg%2F11b6dr1lh8?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>202 Xô Viết Nghệ Tĩnh, Phường 19, Bình Thạnh, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/?utm_source=GMB_list&amp;utm_medium=organic&amp;utm_campaign=GMB_website</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10.798207</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>106.7110781</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.798207,106.7110781,17z/data=!3m1!4b1!4m6!3m5!1s0x317529995cd984f1:0x172cdde6dd91a49!8m2!3d10.798207!4d106.7110781!16s%2Fg%2F11k4zm1m23?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>469 Lê Đại Hành, Phường 11, Quận 11, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10.7687575</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>106.652009</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7687575,106.652009,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f5110eb6b01:0x5c88051ebdbb5ba7!8m2!3d10.7687575!4d106.652009!16s%2Fg%2F11jlvlht8w?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>269 Tân Hòa Đông, P. Phú Thuận, Bình Tân, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10.7600355</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>106.6245446</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7600355,106.6245446,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c28a2e0add3:0x51bc42794e9ff30f!8m2!3d10.7600355!4d106.6245446!16s%2Fg%2F11hbfk0bnv?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>168 Đ. Hiệp Bình, Hiệp Bình Phước, Thủ Đức, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10.8442906</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>106.7305418</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8442906,106.7305418,17z/data=!3m1!4b1!4m6!3m5!1s0x317527da31551f5f:0x194093702147c2c!8m2!3d10.8442906!4d106.7305418!16s%2Fg%2F11gb3pznhq?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>9 Nguyễn Oanh, P. 10, Gò Vấp, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10.8381671</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>106.6753234</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8381671,106.6753234,17z/data=!3m1!4b1!4m6!3m5!1s0x317529ab4616acf7:0xe40f929929676cc8!8m2!3d10.8381671!4d106.6753234!16s%2Fg%2F1pv1ntk4b?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Siêu Thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>688 Đ. Lê Đức Thọ, P. 15, Gò Vấp, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10.8463468</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>106.6707975</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+Th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8463468,106.6707975,17z/data=!3m1!4b1!4m6!3m5!1s0x317529b2193832cb:0xde42c4c0dd4db2d2!8m2!3d10.8463468!4d106.6707975!16s%2Fg%2F11b67rmd7t?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>455 Đ. Tân Kỳ Tân Quý, Tân Quý, Tân Phú, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10.7994742</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>106.619667</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7994742,106.619667,17z/data=!3m1!4b1!4m6!3m5!1s0x3175295792b1242f:0x54f21e80ba26ada6!8m2!3d10.7994742!4d106.619667!16s%2Fg%2F11c1r6r9b2?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>692 Quang Trung, Phường 8, Gò Vấp, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10.8366255</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>106.6581465</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8366255,106.6581465,17z/data=!3m1!4b1!4m6!3m5!1s0x317529a0c9117d23:0xbe6dacc832ae856d!8m2!3d10.8366255!4d106.6581465!16s%2Fg%2F11b6x54p3b?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>154 Đ. Tô Ngọc Vân, Linh Xuân, Thủ Đức, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10.8538283</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>106.7513166</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8538283,106.7513166,17z/data=!3m1!4b1!4m6!3m5!1s0x31752795b77c0ce3:0xec3b8556ec713f58!8m2!3d10.8538283!4d106.7513166!16s%2Fg%2F11bc7rjsl7?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>566 HL2, Kp 6, Bình Tân, Thành phố Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10.7698738</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>106.6130821</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7698738,106.6130821,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c3db69ea487:0xe6a3762a6edf2d7e!8m2!3d10.7698738!4d106.6130821!16s%2Fg%2F11bw1zpkbt?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>55A Đ. Nguyễn Ảnh Thủ, Trung Mỹ Tây, Quận 12, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10.8561081</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>106.6078826</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8561081,106.6078826,17z/data=!3m1!4b1!4m6!3m5!1s0x31752a3f1b2e8bfb:0xb3c9b77dcc25ebc7!8m2!3d10.8561081!4d106.6078826!16s%2Fg%2F11df0vl280?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>287A Đ. Lê Văn Quới, Bình Trị Đông, Bình Tân, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10.7759843</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>106.6126216</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7759843,106.6126216,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c6bb8a5c095:0xcd356e9e80994d43!8m2!3d10.7759843!4d106.6126216!16s%2Fg%2F11hbfhvy7m?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>138B Đ. Gò Dầu, P, Tân Phú, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10.7960212</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>106.6236648</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7960212,106.6236648,17z/data=!3m1!4b1!4m6!3m5!1s0x31752bff29f0f4d7:0x2d1b33549bed5fd8!8m2!3d10.7960212!4d106.6236648!16s%2Fg%2F11cm6s1qwm?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>203 Lã Xuân Oai, Thành phố, Thủ Đức, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10.8400159</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>106.7963723</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8400159,106.7963723,17z/data=!3m1!4b1!4m6!3m5!1s0x31752713de2422ff:0xf510cb27d422f8fe!8m2!3d10.8400159!4d106.7963723!16s%2Fg%2F11c74_j1m4?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>620-622-624, 628 Nguyễn Oanh, Phường 6, Gò Vấp, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10.8496324</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>106.6789428</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8496324,106.6789428,17z/data=!3m1!4b1!4m6!3m5!1s0x3175284c8420765f:0x9fcabb9b951f2d89!8m2!3d10.8496324!4d106.6789428!16s%2Fg%2F11fyx9t40q?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>891 Đ. Nguyễn Văn Tạo, Hiệp Phước, Nhà Bè, Thành phố Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10.6329601</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>106.7357346</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.6329601,106.7357346,17z/data=!3m1!4b1!4m6!3m5!1s0x31753b570e8100e1:0x17fe82fc53b2be9e!8m2!3d10.6329601!4d106.7357346!16s%2Fg%2F11jlvlt287?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1/1A D. Vạn Hạnh 3, Trung Mỹ Tây, Hóc Môn, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10.8648952</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>106.6135797</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8648952,106.6135797,17z/data=!3m1!4b1!4m6!3m5!1s0x31752a11253555dd:0xcec95daee77f857d!8m2!3d10.8648952!4d106.6135797!16s%2Fg%2F11g7cz9sz2?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2044 QL1A, Quận 12, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10.8567149</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>106.6391495</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8567149,106.6391495,17z/data=!3m1!4b1!4m6!3m5!1s0x31752a3108452b11:0x84c6aa5357dff143!8m2!3d10.8567149!4d106.6391495!16s%2Fg%2F11cr_w6v62?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Siêu Thị Điện Thoại Thế Giới Di Động Quận Thủ Đức</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>32 Hoàng Cầm, Linh Xuân, Thủ Đức, Thành phố Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10.8751283</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>106.7659387</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+Th%E1%BB%8B+%C4%90i%E1%BB%87n+Tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+Qu%E1%BA%ADn+Th%E1%BB%A7+%C4%90%E1%BB%A9c/@10.8751283,106.7659387,17z/data=!3m1!4b1!4m6!3m5!1s0x317527fa2bfbbd09:0xbc4aaacaa7ea5248!8m2!3d10.8751283!4d106.7659387!16s%2Fg%2F11g6mr89sd?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>154-156 Lê Văn Thọ, P. 11 Đ. Lê Văn Thọ, Phường 11, Gò Vấp, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10.8414818</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>106.6572998</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8414818,106.6572998,17z/data=!3m1!4b1!4m6!3m5!1s0x317529a3e8e5880f:0xc53ed24fe318935!8m2!3d10.8414818!4d106.6572998!16s%2Fg%2F11c1n5w_z7?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>416 Đ. Bình Long, Tân Quý, Tân Phú, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10.7885599</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>106.6173543</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7885599,106.6173543,17z/data=!3m1!4b1!4m6!3m5!1s0x31752bfa2ec5a2ef:0xf186797113efea9d!8m2!3d10.7885599!4d106.6173543!16s%2Fg%2F11c6qt_3j5?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>838 QL13, Hiệp Bình Phước, Thủ Đức, Hồ Chí Minh 800000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10.8649804</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>106.7244583</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8649804,106.7244583,17z/data=!3m1!4b1!4m6!3m5!1s0x317527fd445a22a7:0x545090444d18ca77!8m2!3d10.8649804!4d106.7244583!16s%2Fg%2F11g8_27w5m?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1208 Kha Vạn Cân, KP. 02, P, Thủ Đức, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10.8610681</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>106.7610568</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8610681,106.7610568,17z/data=!3m1!4b1!4m6!3m5!1s0x3175279adb5bd4d9:0xbdea7a7481f7b4fa!8m2!3d10.8610681!4d106.7610568!16s%2Fg%2F11c2lg38vy?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1527 Nguyễn Cửu Phú, Tân Kiên, Bình Chánh, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>+842838102102</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10.7294433</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>106.581195</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7294433,106.581195,17z/data=!3m1!4b1!4m6!3m5!1s0x31752d78869227c5:0x4ddca2e4a6fe2567!8m2!3d10.7294433!4d106.581195!16s%2Fg%2F11b6x87zsg?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động Thủ Đức</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>340 Đ. Võ Văn Ngân, Phường, Thủ Đức, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10.8494896</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>106.7711583</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+Th%E1%BB%A7+%C4%90%E1%BB%A9c/@10.8494896,106.7711583,17z/data=!3m1!4b1!4m6!3m5!1s0x3175270aa37eeb8d:0x4ba3dba9b14da11b!8m2!3d10.8494896!4d106.7711583!16s%2Fg%2F11gf8c_91c?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Thế giới di động</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>455 Đ. Tân Kỳ Tân Quý, Phú Thọ Hòa, Tân Phú, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10.7994764</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>106.6196854</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+gi%E1%BB%9Bi+di+%C4%91%E1%BB%99ng/@10.7994764,106.6196854,17z/data=!3m1!4b1!4m6!3m5!1s0x31752bf7165b3539:0x37537f4de0707897!8m2!3d10.7994764!4d106.6196854!16s%2Fg%2F11f3m9mcbl?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>316B Đ. Phan Văn Trị, Bình Thạnh, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10.8173088</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>106.6954285</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8173088,106.6954285,17z/data=!3m1!4b1!4m6!3m5!1s0x317528f1fd1a18b1:0xe5c985df6a43bda7!8m2!3d10.8173088!4d106.6954285!16s%2Fg%2F11g6njwz98?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>739 Lê Trọng Tấn, KP2, Bình Tân, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>+84339891958</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10.815552</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>106.6031606</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.815552,106.6031606,17z/data=!3m1!4b1!4m6!3m5!1s0x31752b957a8a401f:0xbf93728775965de8!8m2!3d10.815552!4d106.6031606!16s%2Fg%2F11fxcdcy5v?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>736, HL2/Hương Lộ 2 (ngay/ngã 4 Mã Lò, đối diện bệnh viện, Bình Tân, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>http://thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10.7654584</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>106.6039306</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7654584,106.6039306,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c47130a9997:0x1b1139198e4f685a!8m2!3d10.7654584!4d106.6039306!16s%2Fg%2F11dfh4w75c?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Khu phố 2, Cần Giuộc, Tay Ninh Province 82000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10.6072193</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>106.6714872</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.6072193,106.6714872,17z/data=!3m1!4b1!4m6!3m5!1s0x317536d738e837f9:0xc0479a2a29fc64ed!8m2!3d10.6072193!4d106.6714872!16s%2Fg%2F11g6q24dpn?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>365 Đ. Phan Văn Hớn, Phường, Quận 12, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>10.8339756</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>106.6072149</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8339756,106.6072149,17z/data=!3m1!4b1!4m6!3m5!1s0x31752bca41134245:0xb2e00356cd688113!8m2!3d10.8339756!4d106.6072149!16s%2Fg%2F11bysjrh95?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>349 QL13, Khu Phố 5, Thủ Đức, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>10.8394201</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>106.7153949</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8394201,106.7153949,17z/data=!3m1!4b1!4m6!3m5!1s0x3175287bb07d8369:0x2c09d7fff53d5d91!8m2!3d10.8394201!4d106.7153949!16s%2Fg%2F11xj3zl6v?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bình Đường/100 Đ. Đào Trinh Nhất, P, Dĩ An, Bình Dương, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10.8701011</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>106.7556827</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8701011,106.7556827,17z/data=!3m1!4b1!4m6!3m5!1s0x3175278903c51dd9:0x8cebddffb9e6ec82!8m2!3d10.8701011!4d106.7556827!16s%2Fg%2F11cs3bxkz8?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>129 Hoàng Cầm, Linh Xuân, Thủ Đức, Thành phố Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10.8810649</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>106.7684806</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8810649,106.7684806,17z/data=!3m1!4b1!4m6!3m5!1s0x3174d88bfaf33195:0xfa1fb0aea3a83800!8m2!3d10.8810649!4d106.7684806!16s%2Fg%2F11b67sh7s3?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>744A Tỉnh Lộ 43, P. Bình Chiểu, Q.Thủ Đức, Hồ Chí Minh, 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>10.8724691</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>106.7331624</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8724691,106.7331624,17z/data=!3m1!4b1!4m6!3m5!1s0x3174d81c85992989:0xae1586d80e0e2ff6!8m2!3d10.8724691!4d106.7331624!16s%2Fg%2F11c1p525xy?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>229 Đ. Nguyễn Thị Tú, P, Bình Tân, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10.8154877</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>106.5944418</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8154877,106.5944418,17z/data=!3m1!4b1!4m6!3m5!1s0x31752b97f67e08a3:0xd52a1ad008483c33!8m2!3d10.8154877!4d106.5944418!16s%2Fg%2F11b6x9s77r?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Siêu thị Điện máy XANH</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>55 Hà Huy Giáp, Thạnh Lộc, Quận 12, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>+841900232461</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.dienmayxanh.com/</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10.8540697</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>106.6791666</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%90i%E1%BB%87n+m%C3%A1y+XANH/@10.8540697,106.6791666,17z/data=!3m1!4b1!4m6!3m5!1s0x317529a57f14dbf3:0x1d22366e6f0cae52!8m2!3d10.8540697!4d106.6791666!16s%2Fg%2F11jkmswwf6?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>667 Đ. Lê Văn Việt, Long Thạnh Mỹ, Thủ Đức, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>10.8500598</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>106.811861</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8500598,106.811861,17z/data=!3m1!4b1!4m6!3m5!1s0x3175274cd2cb7829:0xd30532dfd4a74027!8m2!3d10.8500598!4d106.811861!16s%2Fg%2F11sytgwxp0?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>54-56 Đường số 7, P. Phú Thuận, Bình Tân, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Siêu thị Điện máy XANH</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>+842838102102</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/he-thong-sieu-thi-the-gioi-di-dong</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>10.7518756</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>106.6183418</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7518756,106.6183418,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c329de0ce23:0xf5942a9b6548119d!8m2!3d10.7518756!4d106.6183418!16s%2Fg%2F11fwjrmk1g?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TGDD - Nguyễn Văn Nghi</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>362A Đ.Nguyễn Văn Nghi, P.7, Gò Vấp, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>+8418001062</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>10.8249998</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>106.6856004</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/TGDD+-+Nguy%E1%BB%85n+V%C4%83n+Nghi/@10.8249998,106.6856004,17z/data=!3m1!4b1!4m6!3m5!1s0x317528fb018fe2df:0x94a64820ded9cf06!8m2!3d10.8249998!4d106.6856004!16s%2Fg%2F11gf8d64wt?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>354 Lê Văn Khương, KP2, Quận 12, Thành phố Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>10.8765152</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>106.6491452</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8765152,106.6491452,17z/data=!3m1!4b1!4m6!3m5!1s0x317529e9a9dfb115:0xd266fa72bb6358a8!8m2!3d10.8765152!4d106.6491452!16s%2Fg%2F11bztfq3jj?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1615 ĐT825, Khu Phố 5, Bình Tân, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10.7584236</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>106.5796656</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7584236,106.5796656,17z/data=!3m1!4b1!4m6!3m5!1s0x31752cf8dae8e7c1:0x379b580f0be5c49d!8m2!3d10.7584236!4d106.5796656!16s%2Fg%2F11fxb7t6s2?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TGDD - Nguyễn Sơn</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>171 Nguyễn Sơn, P. Phú Thạnh, Q. Tân Phú, Hồ Chí Minh, 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>+8418001060</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10.783309</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>106.6254609</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/TGDD+-+Nguy%E1%BB%85n+S%C6%A1n/@10.783309,106.6254609,17z/data=!3m1!4b1!4m6!3m5!1s0x31752c035dfcb939:0x5a1a8a30f16ffa38!8m2!3d10.783309!4d106.6254609!16s%2Fg%2F11hbfjwdkq?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>171 ĐT745, KP Long Thới, Thuận An, Bình Dương, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10.899332</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>106.6984839</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.899332,106.6984839,17z/data=!3m1!4b1!4m6!3m5!1s0x3174d7bfeb4b232f:0x8c1dedc9421b4f8c!8m2!3d10.899332!4d106.6984839!16s%2Fg%2F11f3nlgm76?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TGDD - Phạm Văn Chiêu</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>232 Đ. Phạm Văn Chiêu, Phường 9, Gò Vấp, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>+8418001060</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10.8490238</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>106.6503068</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/TGDD+-+Ph%E1%BA%A1m+V%C4%83n+Chi%C3%AAu/@10.8490238,106.6503068,17z/data=!3m1!4b1!4m6!3m5!1s0x31752996525688ff:0xbd1d5583da0eeccb!8m2!3d10.8490238!4d106.6503068!16s%2Fg%2F11csr4vfb0?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>5/A1 KDC, Đồng An/4 TL43, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>10.8903785</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>106.7272455</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8903785,106.7272455,17z/data=!3m1!4b1!4m6!3m5!1s0x3174d81c3b2c39ad:0xcbfb141ba58dc96e!8m2!3d10.8903785!4d106.7272455!16s%2Fg%2F11cnm6yk2g?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Siêu thị điện thoại Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1 Hà Huy Giáp, Khu phố 2, Quận 12, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>10.8928065</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>106.6877162</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+%C4%91i%E1%BB%87n+tho%E1%BA%A1i+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8928065,106.6877162,17z/data=!3m1!4b1!4m6!3m5!1s0x3174d7cf5194f0ab:0x83b635960a8f1eb0!8m2!3d10.8928065!4d106.6877162!16s%2Fg%2F11btrrkm_v?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>23 Đ. Nguyễn Thị Tú, Ấp 4, Bình Chánh, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>10.8136719</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>106.5797225</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8136719,106.5797225,17z/data=!3m1!4b1!4m6!3m5!1s0x31752b9604fd4a0b:0x71f1e0c652572053!8m2!3d10.8136719!4d106.5797225!16s%2Fg%2F11dxb1vbgb?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1 Nguyễn Kiệm, Phường 9, Phú Nhuận, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/tin-tuc/sieu-thi-the-gioi-di-dong-1a-nguyen-kiem-quan-go-v-558539</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>10.814528</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>106.678448</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.814528,106.678448,17z/data=!3m1!4b1!4m6!3m5!1s0x317528d70b9f0317:0x609a8686f4b0fbb3!8m2!3d10.814528!4d106.678448!16s%2Fg%2F11c5sbcbxr?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>361 Đ. Tên Lửa, P, Bình Tân, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>10.752168</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>106.6101083</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.752168,106.6101083,17z/data=!3m1!4b1!4m6!3m5!1s0x31752dc1bd8e3d8b:0x531f1488470eb7d7!8m2!3d10.752168!4d106.6101083!16s%2Fg%2F11rhv_6gb8?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>A4/15, ấp 1, Bình Chánh, Hồ Chí Minh 700000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>10.7887487</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>106.515009</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7887487,106.515009,17z/data=!3m1!4b1!4m6!3m5!1s0x310ad35cc8c6c01b:0x223aa05b6ab9bc22!8m2!3d10.7887487!4d106.515009!16s%2Fg%2F11fx7vbxpb?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>427 Đ. Kinh Dương Vương, Khu Phố 6, Bình Tân, Thành phố Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/?utm_source=GMB_list&amp;utm_medium=organic&amp;utm_campaign=GMB_website</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>10.7392357</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>106.6164188</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.7392357,106.6164188,17z/data=!3m1!4b1!4m6!3m5!1s0x31752d7f45377a8b:0xaa2c07e562726f05!8m2!3d10.7392357!4d106.6164188!16s%2Fg%2F11k4zmjrtk?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động Tỉnh lộ 10</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1306 ĐT825, Tân Tạo, Bình Tân, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>10.7563147</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>106.592861</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng+T%E1%BB%89nh+l%E1%BB%99+10/@10.7563147,106.592861,17z/data=!3m1!4b1!4m6!3m5!1s0x31752d940068cd8b:0x28c119415c86b097!8m2!3d10.7563147!4d106.592861!16s%2Fg%2F11fmyjznts?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1/25A Thủ Khoa Huân, Hòa Lân 1, Thuận An, Bình Dương, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>10.9561303</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>106.7019727</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.9561303,106.7019727,17z/data=!3m1!4b1!4m6!3m5!1s0x3174d749ba759755:0x135adc31f8c8a112!8m2!3d10.9561303!4d106.7019727!16s%2Fg%2F11b7hmjny1?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>728 Đ. Phan Văn Hớn, Ấp 7, Hóc Môn, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>10.850953</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>106.5865045</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.850953,106.5865045,17z/data=!3m1!4b1!4m6!3m5!1s0x31752a50ba6f7eb3:0x3cf3064ceb0c0db5!8m2!3d10.850953!4d106.5865045!16s%2Fg%2F11jn639mf4?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>siêu thị thế giới di động ở sài gòn</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Siêu thị Thế Giới Di Động</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>8 Đường Thới Hòa, ấp 5, Bình Chánh, Hồ Chí Minh 70000, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>+841900232460</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>http://www.thegioididong.com/</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>10.8289322</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>106.5833428</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+Th%E1%BA%BF+Gi%E1%BB%9Bi+Di+%C4%90%E1%BB%99ng/@10.8289322,106.5833428,17z/data=!3m1!4b1!4m6!3m5!1s0x31752b4bf26c9213:0xd4f38a2d63d39efa!8m2!3d10.8289322!4d106.5833428!16s%2Fg%2F11q1p_8f_g?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxNy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
